--- a/payroll/2026/excel/20260910-0911.xlsx
+++ b/payroll/2026/excel/20260910-0911.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\lubaoqiang\git\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFC4302-CD49-4F71-8BBB-C46B0832E5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31118EEC-4C55-46E1-8AAE-F844B70FE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="310" windowWidth="22600" windowHeight="13960" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24890" windowHeight="14620" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
   <sheets>
     <sheet name="产出" sheetId="1" r:id="rId1"/>
@@ -258,105 +258,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">0908-0909 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>集体产出</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4,728 ( </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>实际分配</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4688 ) 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>行会账户</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">A   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>往期结存</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (  3,313 + 261 -</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>舞动乾坤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="19.8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>88-350  = 3,136 )</t>
-    </r>
+    <t>0910-0911 集体产出 4,728 ( 实际分配 4688 ) 
+行会账户A   往期结存 (  3,313 + 261 -舞动乾坤88-350  = 3,136 )</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -364,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,12 +318,6 @@
     </font>
     <font>
       <b/>
-      <sz val="19.8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -434,8 +331,8 @@
     </font>
     <font>
       <b/>
-      <sz val="19.8"/>
-      <name val="宋体"/>
+      <sz val="14"/>
+      <name val="等线 Light"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -558,7 +455,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -567,34 +464,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1116,7 +993,7 @@
     <col min="10" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="66.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="11" t="s">
         <v>69</v>
       </c>
@@ -1933,12 +1810,12 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B36:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
